--- a/March 2026.xlsx
+++ b/March 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abutalib/Projects/personal-accounting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1F3206-74F2-1C4A-95D1-E284727B1A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1CC13BD-4248-7640-A6C1-4BAFA53DC974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="680" windowWidth="30240" windowHeight="17780" xr2:uid="{7E62CB60-3E82-0E48-87C0-051D0E492E72}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17780" xr2:uid="{7E62CB60-3E82-0E48-87C0-051D0E492E72}"/>
   </bookViews>
   <sheets>
     <sheet name="مصاريف الشهر" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="132">
   <si>
     <t>فاتورة الكهرباء</t>
   </si>
@@ -424,6 +424,15 @@
   </si>
   <si>
     <t>كنبة</t>
+  </si>
+  <si>
+    <t>كفر الأودي الأمامي</t>
+  </si>
+  <si>
+    <t>tamara</t>
+  </si>
+  <si>
+    <t>تحويلمتأخر لتكمو</t>
   </si>
 </sst>
 </file>
@@ -437,7 +446,7 @@
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -472,8 +481,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -488,19 +504,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +552,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -553,24 +563,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -927,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C2F52D6-F91F-A540-B517-60C5A16A2B32}">
-  <dimension ref="A1:AF45"/>
+  <dimension ref="A1:AF46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="22" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -951,17 +962,18 @@
     <col min="19" max="19" width="18.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="6.5" style="3" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="0.6640625" customWidth="1"/>
-    <col min="22" max="22" width="24.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="21.33203125" style="3" customWidth="1"/>
+    <col min="23" max="23" width="24.1640625" style="3" customWidth="1"/>
     <col min="24" max="24" width="0.6640625" customWidth="1"/>
     <col min="25" max="25" width="23.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.83203125" style="3" customWidth="1"/>
-    <col min="27" max="27" width="15.1640625" style="3" customWidth="1"/>
-    <col min="28" max="28" width="0.6640625" customWidth="1"/>
-    <col min="29" max="29" width="17" style="3" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="10.83203125" style="3"/>
+    <col min="26" max="26" width="7.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="0.5" customWidth="1"/>
+    <col min="29" max="29" width="17" style="3" customWidth="1"/>
+    <col min="30" max="30" width="7.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.33203125" style="3" customWidth="1"/>
+    <col min="32" max="32" width="9.1640625" style="3" customWidth="1"/>
+    <col min="33" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.3">
@@ -972,14 +984,14 @@
       <c r="D1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19" t="s">
+      <c r="F1" s="16"/>
+      <c r="G1" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="19"/>
+      <c r="H1" s="16"/>
       <c r="I1" s="4"/>
       <c r="J1" s="3" t="s">
         <v>17</v>
@@ -1024,7 +1036,7 @@
       </c>
       <c r="O2" s="3">
         <f>SUM(O7:O26)</f>
-        <v>3974</v>
+        <v>3638</v>
       </c>
       <c r="R2" s="4"/>
       <c r="S2" s="3" t="s">
@@ -1040,15 +1052,15 @@
       </c>
       <c r="W2" s="3">
         <f>SUM(W7:W16)</f>
-        <v>12771</v>
+        <v>15380</v>
       </c>
       <c r="X2" s="4"/>
       <c r="Y2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="AA2" s="3">
-        <f>SUM(AA7:AB41)</f>
-        <v>27780</v>
+        <f>SUM(AA7:AB35)</f>
+        <v>28659</v>
       </c>
       <c r="AB2" s="4"/>
       <c r="AC2" s="3" t="s">
@@ -1056,7 +1068,7 @@
       </c>
       <c r="AD2" s="3">
         <f>SUM(AD7:AD21)</f>
-        <v>2537</v>
+        <v>2892</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
@@ -1070,11 +1082,11 @@
       </c>
       <c r="E3" s="3">
         <f>SUM(E7:E25)</f>
-        <v>1476</v>
+        <v>2007</v>
       </c>
       <c r="F3" s="3">
         <f>SUM(F7:F28)</f>
-        <v>5876</v>
+        <v>5645</v>
       </c>
       <c r="G3" s="3">
         <f>SUM(G7:G25)</f>
@@ -1095,7 +1107,7 @@
       </c>
       <c r="AD3" s="3">
         <f>AA21-AD2</f>
-        <v>428</v>
+        <v>-227</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
@@ -1113,11 +1125,11 @@
       </c>
       <c r="G4" s="3">
         <f>E5</f>
-        <v>150</v>
+        <v>-45</v>
       </c>
       <c r="H4" s="3">
         <f>F5</f>
-        <v>3151</v>
+        <v>3382</v>
       </c>
       <c r="I4" s="4"/>
       <c r="R4" s="4"/>
@@ -1133,19 +1145,19 @@
       </c>
       <c r="E5" s="3">
         <f>E4-O2-E3</f>
-        <v>150</v>
+        <v>-45</v>
       </c>
       <c r="F5" s="3">
         <f>F4-F3</f>
-        <v>3151</v>
+        <v>3382</v>
       </c>
       <c r="G5" s="3">
         <f>G4-G3</f>
-        <v>150</v>
+        <v>-45</v>
       </c>
       <c r="H5" s="3">
         <f>H4-H3</f>
-        <v>556</v>
+        <v>787</v>
       </c>
       <c r="I5" s="4"/>
       <c r="R5" s="4"/>
@@ -1172,10 +1184,10 @@
       <c r="O6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="18" t="s">
+      <c r="P6" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="Q6" s="18"/>
+      <c r="Q6" s="15"/>
       <c r="R6" s="9"/>
       <c r="U6" s="9"/>
       <c r="X6" s="9"/>
@@ -1201,14 +1213,11 @@
       </c>
       <c r="M7" s="3">
         <f>SUM(N7:O7)</f>
-        <v>470</v>
+        <v>134</v>
       </c>
       <c r="O7" s="3">
         <f>SUM(P7:Q7)</f>
-        <v>470</v>
-      </c>
-      <c r="P7" s="3">
-        <v>336</v>
+        <v>134</v>
       </c>
       <c r="Q7" s="3">
         <v>134</v>
@@ -1239,13 +1248,13 @@
       <c r="AC7" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="AD7" s="11">
+      <c r="AD7" s="18">
         <v>1580</v>
       </c>
       <c r="AE7" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="AF7" s="12"/>
+      <c r="AF7" s="10"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -1258,7 +1267,7 @@
       <c r="D8" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F8" s="3">
+      <c r="E8" s="3">
         <v>531</v>
       </c>
       <c r="I8" s="4"/>
@@ -1298,12 +1307,15 @@
       <c r="Y8" s="1" t="s">
         <v>67</v>
       </c>
+      <c r="Z8" s="3">
+        <v>1500</v>
+      </c>
       <c r="AB8" s="4"/>
       <c r="AC8" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="AD8" s="11">
-        <v>450</v>
+      <c r="AD8" s="18">
+        <v>350</v>
       </c>
       <c r="AE8" s="3" t="s">
         <v>88</v>
@@ -1320,7 +1332,7 @@
       <c r="D9" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>300</v>
       </c>
       <c r="I9" s="4"/>
@@ -1350,21 +1362,21 @@
       </c>
       <c r="W9" s="3">
         <f>H5</f>
-        <v>556</v>
+        <v>787</v>
       </c>
       <c r="X9" s="4"/>
       <c r="Y9" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AA9" s="11">
+      <c r="AA9" s="18">
         <f>SUM(Z7:Z8)</f>
-        <v>800</v>
+        <v>2300</v>
       </c>
       <c r="AB9" s="4"/>
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD9" s="11">
+      <c r="AD9" s="18">
         <v>80</v>
       </c>
       <c r="AE9" s="3" t="s">
@@ -1402,14 +1414,15 @@
         <v>55</v>
       </c>
       <c r="W10" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="X10" s="4"/>
+      <c r="AA10" s="17"/>
       <c r="AB10" s="4"/>
       <c r="AC10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD10" s="11">
+      <c r="AD10" s="18">
         <v>80</v>
       </c>
       <c r="AE10" s="3" t="s">
@@ -1447,20 +1460,20 @@
         <v>56</v>
       </c>
       <c r="W11" s="3">
-        <v>313</v>
+        <v>27</v>
       </c>
       <c r="X11" s="4"/>
       <c r="Y11" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AA11" s="11">
+      <c r="AA11" s="18">
         <v>3000</v>
       </c>
       <c r="AB11" s="4"/>
       <c r="AC11" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="AD11" s="11">
+      <c r="AD11" s="18">
         <v>120</v>
       </c>
       <c r="AE11" s="3" t="s">
@@ -1499,9 +1512,10 @@
       </c>
       <c r="W12" s="3">
         <f>J32</f>
-        <v>7352</v>
+        <v>11516</v>
       </c>
       <c r="X12" s="4"/>
+      <c r="AA12" s="17"/>
       <c r="AB12" s="4"/>
       <c r="AC12" s="3" t="s">
         <v>11</v>
@@ -1544,7 +1558,7 @@
       <c r="Y13" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AA13" s="11">
+      <c r="AA13" s="18">
         <v>1000</v>
       </c>
       <c r="AB13" s="4"/>
@@ -1586,8 +1600,17 @@
       <c r="R14" s="4"/>
       <c r="U14" s="4"/>
       <c r="X14" s="4"/>
+      <c r="AA14" s="17"/>
       <c r="AB14" s="4"/>
-      <c r="AC14" s="1"/>
+      <c r="AC14" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD14" s="18">
+        <v>154</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
@@ -1624,7 +1647,17 @@
         <f>K27</f>
         <v>1892</v>
       </c>
+      <c r="AA15" s="17"/>
       <c r="AB15" s="4"/>
+      <c r="AC15" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD15" s="18">
+        <v>301</v>
+      </c>
+      <c r="AE15" s="3" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.3">
       <c r="C16" s="4"/>
@@ -1654,6 +1687,7 @@
       <c r="Z16" s="3">
         <v>1000</v>
       </c>
+      <c r="AA16" s="17"/>
       <c r="AB16" s="4"/>
     </row>
     <row r="17" spans="3:28" x14ac:dyDescent="0.3">
@@ -1662,7 +1696,7 @@
         <v>45</v>
       </c>
       <c r="E17" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="3" t="s">
@@ -1682,8 +1716,9 @@
         <v>68</v>
       </c>
       <c r="Z17" s="3">
-        <v>300</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="17"/>
       <c r="AB17" s="4"/>
     </row>
     <row r="18" spans="3:28" x14ac:dyDescent="0.3">
@@ -1695,7 +1730,7 @@
         <v>350</v>
       </c>
       <c r="I18" s="4"/>
-      <c r="J18" s="17" t="s">
+      <c r="J18" s="14" t="s">
         <v>11</v>
       </c>
       <c r="K18" s="3">
@@ -1714,6 +1749,7 @@
       <c r="Z18" s="3">
         <v>-150</v>
       </c>
+      <c r="AA18" s="17"/>
       <c r="AB18" s="4"/>
     </row>
     <row r="19" spans="3:28" x14ac:dyDescent="0.3">
@@ -1738,6 +1774,7 @@
       <c r="Z19" s="3">
         <v>-77</v>
       </c>
+      <c r="AA19" s="17"/>
       <c r="AB19" s="4"/>
     </row>
     <row r="20" spans="3:28" x14ac:dyDescent="0.3">
@@ -1762,6 +1799,7 @@
       <c r="R20" s="4"/>
       <c r="U20" s="4"/>
       <c r="X20" s="4"/>
+      <c r="AA20" s="17"/>
       <c r="AB20" s="4"/>
     </row>
     <row r="21" spans="3:28" x14ac:dyDescent="0.3">
@@ -1774,7 +1812,7 @@
         <v>595</v>
       </c>
       <c r="I21" s="4"/>
-      <c r="J21" s="17" t="s">
+      <c r="J21" s="14" t="s">
         <v>14</v>
       </c>
       <c r="K21" s="3">
@@ -1790,9 +1828,9 @@
       <c r="Y21" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="AA21" s="11">
+      <c r="AA21" s="18">
         <f>SUM(Z15:Z20)</f>
-        <v>2965</v>
+        <v>2665</v>
       </c>
       <c r="AB21" s="4"/>
     </row>
@@ -1812,6 +1850,7 @@
       <c r="R22" s="4"/>
       <c r="U22" s="4"/>
       <c r="X22" s="4"/>
+      <c r="AA22" s="17"/>
       <c r="AB22" s="4"/>
     </row>
     <row r="23" spans="3:28" x14ac:dyDescent="0.3">
@@ -1833,7 +1872,7 @@
       <c r="Y23" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="AA23" s="11">
+      <c r="AA23" s="18">
         <f>L27</f>
         <v>820</v>
       </c>
@@ -1855,6 +1894,7 @@
       <c r="R24" s="4"/>
       <c r="U24" s="4"/>
       <c r="X24" s="4"/>
+      <c r="AA24" s="17"/>
       <c r="AB24" s="4"/>
     </row>
     <row r="25" spans="3:28" x14ac:dyDescent="0.3">
@@ -1876,7 +1916,7 @@
       <c r="Y25" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="AA25" s="11">
+      <c r="AA25" s="18">
         <v>2000</v>
       </c>
       <c r="AB25" s="4"/>
@@ -1897,6 +1937,7 @@
       <c r="R26" s="3"/>
       <c r="U26" s="3"/>
       <c r="X26" s="3"/>
+      <c r="AA26" s="17"/>
       <c r="AB26" s="3"/>
     </row>
     <row r="27" spans="3:28" x14ac:dyDescent="0.3">
@@ -1915,7 +1956,7 @@
       </c>
       <c r="M27" s="3">
         <f>SUM(M7:M25)</f>
-        <v>1235</v>
+        <v>899</v>
       </c>
       <c r="N27" s="3">
         <f>SUM(N7:N25)</f>
@@ -1927,7 +1968,7 @@
       <c r="Y27" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AA27" s="13">
+      <c r="AA27" s="19">
         <f>T2</f>
         <v>595</v>
       </c>
@@ -1939,6 +1980,7 @@
       <c r="R28" s="3"/>
       <c r="U28" s="3"/>
       <c r="X28" s="3"/>
+      <c r="AA28" s="17"/>
       <c r="AB28" s="3"/>
     </row>
     <row r="29" spans="3:28" x14ac:dyDescent="0.3">
@@ -1950,9 +1992,9 @@
       <c r="Y29" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="AA29" s="11">
+      <c r="AA29" s="20">
         <f>M27</f>
-        <v>1235</v>
+        <v>899</v>
       </c>
       <c r="AB29" s="3"/>
     </row>
@@ -1962,11 +2004,12 @@
       <c r="R30" s="3"/>
       <c r="U30" s="3"/>
       <c r="X30" s="3"/>
+      <c r="AA30" s="17"/>
       <c r="AB30" s="3"/>
     </row>
     <row r="31" spans="3:28" ht="46" x14ac:dyDescent="0.3">
       <c r="C31" s="3"/>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="13" t="s">
         <v>112</v>
       </c>
       <c r="E31" s="3" t="s">
@@ -1991,16 +2034,16 @@
       <c r="Y31" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="AA31" s="10">
+      <c r="AA31" s="17">
         <f>W2</f>
-        <v>12771</v>
+        <v>15380</v>
       </c>
       <c r="AB31" s="3"/>
     </row>
     <row r="32" spans="3:28" x14ac:dyDescent="0.3">
       <c r="C32" s="3"/>
       <c r="D32">
-        <v>21371</v>
+        <v>20221</v>
       </c>
       <c r="E32" s="3" t="e">
         <f>D32+#REF!</f>
@@ -2009,128 +2052,157 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3">
         <f>الأرصدة!M29-'مصاريف الشهر'!D32</f>
-        <v>7352</v>
+        <v>11516</v>
       </c>
       <c r="O32" s="3">
         <f>E3</f>
-        <v>1476</v>
+        <v>2007</v>
       </c>
       <c r="P32" s="3">
         <f>F3</f>
-        <v>5876</v>
+        <v>5645</v>
       </c>
       <c r="Q32" s="3">
         <f>J32-SUM(O32:P32)</f>
-        <v>0</v>
+        <v>3864</v>
       </c>
       <c r="R32" s="3"/>
       <c r="U32" s="3"/>
       <c r="X32" s="3"/>
+      <c r="AA32" s="17"/>
       <c r="AB32" s="3"/>
     </row>
     <row r="33" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="C33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="R33" s="3"/>
-      <c r="U33" s="3"/>
-      <c r="X33" s="3"/>
       <c r="Y33" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA33" s="17"/>
+    </row>
+    <row r="34" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="Y34" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="17"/>
+    </row>
+    <row r="35" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="AA35" s="17">
+        <f>SUM(Z34:Z34)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="Y36" s="4"/>
+      <c r="Z36" s="4"/>
+      <c r="AA36" s="4"/>
+    </row>
+    <row r="37" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="Y37" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z37" s="3">
+        <v>150</v>
+      </c>
+      <c r="AA37" s="17"/>
+    </row>
+    <row r="38" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="Y38" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z38" s="3">
+        <v>77</v>
+      </c>
+      <c r="AA38" s="17"/>
+    </row>
+    <row r="39" spans="3:28" ht="46" x14ac:dyDescent="0.3">
+      <c r="Y39" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA39" s="17">
+        <f>SUM(Z37:Z38)</f>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="40" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="Y40" s="13"/>
+      <c r="AA40" s="17"/>
+    </row>
+    <row r="41" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="C41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="R41" s="3"/>
+      <c r="U41" s="3"/>
+      <c r="X41" s="3"/>
+      <c r="Y41" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="Z41" s="3">
         <v>2000</v>
       </c>
-      <c r="AB33" s="3"/>
-    </row>
-    <row r="34" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="C34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="R34" s="3"/>
-      <c r="U34" s="3"/>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="3" t="s">
+      <c r="AA41" s="17"/>
+      <c r="AB41" s="3"/>
+    </row>
+    <row r="42" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="C42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="R42" s="3"/>
+      <c r="U42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Z34" s="3">
+      <c r="Z42" s="3">
         <f>G5</f>
-        <v>150</v>
-      </c>
-      <c r="AB34" s="3"/>
-    </row>
-    <row r="35" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="C35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="R35" s="3"/>
-      <c r="U35" s="3"/>
-      <c r="X35" s="3"/>
-      <c r="Y35" s="3" t="s">
+        <v>-45</v>
+      </c>
+      <c r="AA42" s="17"/>
+      <c r="AB42" s="3"/>
+    </row>
+    <row r="43" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="C43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="R43" s="3"/>
+      <c r="U43" s="3"/>
+      <c r="X43" s="3"/>
+      <c r="Y43" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="Z35" s="3">
-        <v>-56</v>
-      </c>
-      <c r="AB35" s="3"/>
-    </row>
-    <row r="36" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="C36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="R36" s="3"/>
-      <c r="U36" s="3"/>
-      <c r="X36" s="3"/>
-      <c r="AB36" s="3"/>
-    </row>
-    <row r="37" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="Y37" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA37" s="10">
-        <f>SUM(Z33:Z35)</f>
-        <v>2094</v>
-      </c>
-    </row>
-    <row r="39" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="Y39" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="Y40" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z40" s="3">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="41" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="AA41" s="11">
-        <f>SUM(Z40:Z40)</f>
-        <v>500</v>
-      </c>
-    </row>
-    <row r="43" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="Y43" s="17" t="s">
-        <v>14</v>
-      </c>
       <c r="Z43" s="3">
-        <v>150</v>
-      </c>
+        <f>-Z17</f>
+        <v>0</v>
+      </c>
+      <c r="AA43" s="17"/>
+      <c r="AB43" s="3"/>
     </row>
     <row r="44" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="Y44" s="17" t="s">
-        <v>11</v>
+      <c r="C44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="R44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="X44" s="3"/>
+      <c r="Y44" s="3" t="s">
+        <v>131</v>
       </c>
       <c r="Z44" s="3">
-        <v>77</v>
-      </c>
+        <f>AA39</f>
+        <v>227</v>
+      </c>
+      <c r="AA44" s="17"/>
+      <c r="AB44" s="3"/>
     </row>
     <row r="45" spans="3:28" x14ac:dyDescent="0.3">
       <c r="Y45" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA45" s="11">
-        <f>SUM(Z43:Z44)</f>
-        <v>227</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="AA45" s="17">
+        <f>SUM(Z41:Z44)</f>
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="46" spans="3:28" x14ac:dyDescent="0.3">
+      <c r="AA46" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2221,37 +2293,37 @@
         <v>51</v>
       </c>
       <c r="B2" s="2"/>
-      <c r="C2" s="14">
+      <c r="C2" s="11">
         <f>SUM(D6:D19)</f>
-        <v>7650</v>
+        <v>10700</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
       <c r="F2" s="3">
         <f>SUM(G6:G19)</f>
-        <v>-27</v>
+        <v>0</v>
       </c>
       <c r="H2" s="4"/>
-      <c r="I2" s="14">
+      <c r="I2" s="11">
         <f>SUM(J6:J11)</f>
         <v>5300</v>
       </c>
       <c r="K2" s="4"/>
-      <c r="L2" s="14">
+      <c r="L2" s="11">
         <f>SUM(M6:M13)</f>
         <v>3008</v>
       </c>
       <c r="N2" s="4"/>
-      <c r="O2" s="14">
+      <c r="O2" s="11">
         <f>SUM(P6:P20)</f>
-        <v>60265</v>
+        <v>61052</v>
       </c>
       <c r="Q2" s="4"/>
-      <c r="R2" s="14">
-        <f>SUM(T6:T16)</f>
-        <v>26373</v>
-      </c>
-      <c r="S2" s="14"/>
+      <c r="R2" s="11">
+        <f>SUM(T6:T19)</f>
+        <v>27223</v>
+      </c>
+      <c r="S2" s="11"/>
       <c r="U2" s="2"/>
     </row>
     <row r="3" spans="1:21" ht="22" x14ac:dyDescent="0.3">
@@ -2259,7 +2331,7 @@
         <v>48</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="C3" s="14">
+      <c r="C3" s="11">
         <v>3050</v>
       </c>
       <c r="D3" s="3"/>
@@ -2290,7 +2362,7 @@
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="11">
         <v>17750</v>
       </c>
       <c r="E4" s="4"/>
@@ -2314,7 +2386,7 @@
     <row r="5" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="B5" s="2"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="14"/>
+      <c r="D5" s="11"/>
       <c r="E5" s="4"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -2338,35 +2410,35 @@
       <c r="C6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="11">
         <v>19300</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="11">
         <v>-653</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="11">
         <v>2600</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6" s="11">
         <v>3448</v>
       </c>
       <c r="N6" s="4"/>
       <c r="O6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="P6" s="14">
+      <c r="P6" s="11">
         <v>39948</v>
       </c>
       <c r="Q6" s="4"/>
@@ -2376,7 +2448,7 @@
       <c r="S6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="T6" s="14">
+      <c r="T6" s="11">
         <v>187</v>
       </c>
       <c r="U6" s="2"/>
@@ -2386,33 +2458,33 @@
       <c r="C7" s="3">
         <v>1</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="11">
         <v>-17750</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="3">
         <v>1</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="11">
         <v>313</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="11">
         <v>800</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="3">
         <v>1</v>
       </c>
-      <c r="M7" s="14"/>
+      <c r="M7" s="11"/>
       <c r="N7" s="4"/>
       <c r="O7" s="3">
         <v>1</v>
       </c>
-      <c r="P7" s="14">
+      <c r="P7" s="11">
         <v>864</v>
       </c>
       <c r="Q7" s="4"/>
@@ -2422,7 +2494,7 @@
       <c r="S7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="T7" s="14">
+      <c r="T7" s="11">
         <v>1083</v>
       </c>
       <c r="U7" s="2"/>
@@ -2432,35 +2504,35 @@
       <c r="C8" s="3">
         <v>1</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="11">
         <v>3050</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="3">
         <v>2</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="11">
         <v>313</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="11">
         <v>1000</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="3">
         <v>2</v>
       </c>
-      <c r="M8" s="14">
+      <c r="M8" s="11">
         <v>2000</v>
       </c>
       <c r="N8" s="4"/>
       <c r="O8" s="3">
         <v>1</v>
       </c>
-      <c r="P8" s="14">
+      <c r="P8" s="11">
         <v>17777</v>
       </c>
       <c r="Q8" s="4"/>
@@ -2470,7 +2542,7 @@
       <c r="S8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="T8" s="14">
+      <c r="T8" s="11">
         <v>721</v>
       </c>
       <c r="U8" s="2"/>
@@ -2480,33 +2552,35 @@
       <c r="C9" s="3">
         <v>2</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="11">
         <v>3050</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="3">
         <v>3</v>
       </c>
-      <c r="G9" s="14"/>
+      <c r="G9" s="11">
+        <v>27</v>
+      </c>
       <c r="H9" s="4"/>
       <c r="I9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="11">
         <v>500</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="3">
         <v>3</v>
       </c>
-      <c r="M9" s="14">
+      <c r="M9" s="11">
         <v>-2440</v>
       </c>
       <c r="N9" s="4"/>
       <c r="O9" s="3">
         <v>2</v>
       </c>
-      <c r="P9" s="14">
+      <c r="P9" s="11">
         <v>1676</v>
       </c>
       <c r="Q9" s="4"/>
@@ -2516,7 +2590,7 @@
       <c r="S9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="14">
+      <c r="T9" s="11">
         <v>4479</v>
       </c>
       <c r="U9" s="2"/>
@@ -2526,25 +2600,31 @@
       <c r="C10" s="3">
         <v>3</v>
       </c>
-      <c r="D10" s="14"/>
+      <c r="D10" s="11">
+        <v>3050</v>
+      </c>
       <c r="E10" s="4"/>
       <c r="F10" s="3">
         <v>4</v>
       </c>
-      <c r="G10" s="14"/>
+      <c r="G10" s="11"/>
       <c r="H10" s="4"/>
       <c r="I10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="11">
         <v>400</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="3"/>
-      <c r="M10" s="14"/>
+      <c r="M10" s="11"/>
       <c r="N10" s="4"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="14"/>
+      <c r="O10" s="3">
+        <v>3</v>
+      </c>
+      <c r="P10" s="11">
+        <v>787</v>
+      </c>
       <c r="Q10" s="4"/>
       <c r="R10">
         <v>1</v>
@@ -2552,7 +2632,7 @@
       <c r="S10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="T10" s="14">
+      <c r="T10" s="11">
         <v>540</v>
       </c>
       <c r="U10" s="2"/>
@@ -2562,23 +2642,23 @@
       <c r="C11" s="3">
         <v>4</v>
       </c>
-      <c r="D11" s="14"/>
+      <c r="D11" s="11"/>
       <c r="E11" s="4"/>
       <c r="F11" s="3">
         <v>5</v>
       </c>
-      <c r="G11" s="14"/>
+      <c r="G11" s="11"/>
       <c r="H11" s="4"/>
       <c r="I11" s="3"/>
-      <c r="J11" s="14"/>
+      <c r="J11" s="11"/>
       <c r="K11" s="4"/>
       <c r="L11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M11" s="14"/>
+      <c r="M11" s="11"/>
       <c r="N11" s="4"/>
       <c r="O11" s="3"/>
-      <c r="P11" s="14"/>
+      <c r="P11" s="11"/>
       <c r="Q11" s="4"/>
       <c r="R11">
         <v>1</v>
@@ -2586,7 +2666,7 @@
       <c r="S11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="T11" s="14">
+      <c r="T11" s="11">
         <v>3162</v>
       </c>
       <c r="U11" s="2"/>
@@ -2596,23 +2676,23 @@
       <c r="C12" s="3">
         <v>5</v>
       </c>
-      <c r="D12" s="14"/>
+      <c r="D12" s="11"/>
       <c r="E12" s="4"/>
       <c r="F12" s="3">
         <v>6</v>
       </c>
-      <c r="G12" s="14"/>
+      <c r="G12" s="11"/>
       <c r="H12" s="4"/>
       <c r="I12" s="3"/>
-      <c r="J12" s="14"/>
+      <c r="J12" s="11"/>
       <c r="K12" s="4"/>
       <c r="L12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="M12" s="14"/>
+      <c r="M12" s="11"/>
       <c r="N12" s="4"/>
       <c r="O12" s="3"/>
-      <c r="P12" s="14"/>
+      <c r="P12" s="11"/>
       <c r="Q12" s="4"/>
       <c r="R12">
         <v>2</v>
@@ -2620,7 +2700,7 @@
       <c r="S12" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="T12" s="14">
+      <c r="T12" s="11">
         <v>10000</v>
       </c>
       <c r="U12" s="2"/>
@@ -2630,23 +2710,23 @@
       <c r="C13" s="3">
         <v>6</v>
       </c>
-      <c r="D13" s="14"/>
+      <c r="D13" s="11"/>
       <c r="E13" s="4"/>
       <c r="F13" s="3">
         <v>7</v>
       </c>
-      <c r="G13" s="14"/>
+      <c r="G13" s="11"/>
       <c r="H13" s="4"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="14"/>
+      <c r="J13" s="11"/>
       <c r="K13" s="4"/>
       <c r="L13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M13" s="14"/>
+      <c r="M13" s="11"/>
       <c r="N13" s="4"/>
       <c r="O13" s="3"/>
-      <c r="P13" s="14"/>
+      <c r="P13" s="11"/>
       <c r="Q13" s="4"/>
       <c r="R13">
         <v>2</v>
@@ -2654,7 +2734,7 @@
       <c r="S13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="T13" s="14">
+      <c r="T13" s="11">
         <v>1000</v>
       </c>
       <c r="U13" s="2"/>
@@ -2664,21 +2744,21 @@
       <c r="C14" s="3">
         <v>7</v>
       </c>
-      <c r="D14" s="14"/>
+      <c r="D14" s="11"/>
       <c r="E14" s="4"/>
       <c r="F14" s="3">
         <v>8</v>
       </c>
-      <c r="G14" s="14"/>
+      <c r="G14" s="11"/>
       <c r="H14" s="4"/>
       <c r="I14" s="3"/>
-      <c r="J14" s="14"/>
+      <c r="J14" s="11"/>
       <c r="K14" s="4"/>
       <c r="L14" s="3"/>
-      <c r="M14" s="14"/>
+      <c r="M14" s="11"/>
       <c r="N14" s="4"/>
       <c r="O14" s="3"/>
-      <c r="P14" s="14"/>
+      <c r="P14" s="11"/>
       <c r="Q14" s="4"/>
       <c r="R14">
         <v>2</v>
@@ -2686,7 +2766,7 @@
       <c r="S14" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="T14" s="14">
+      <c r="T14" s="11">
         <v>500</v>
       </c>
       <c r="U14" s="2"/>
@@ -2696,21 +2776,21 @@
       <c r="C15" s="3">
         <v>8</v>
       </c>
-      <c r="D15" s="14"/>
+      <c r="D15" s="11"/>
       <c r="E15" s="4"/>
       <c r="F15" s="3">
         <v>9</v>
       </c>
-      <c r="G15" s="14"/>
+      <c r="G15" s="11"/>
       <c r="H15" s="4"/>
       <c r="I15" s="3"/>
-      <c r="J15" s="14"/>
+      <c r="J15" s="11"/>
       <c r="K15" s="4"/>
       <c r="L15" s="3"/>
-      <c r="M15" s="14"/>
+      <c r="M15" s="11"/>
       <c r="N15" s="4"/>
       <c r="O15" s="3"/>
-      <c r="P15" s="14"/>
+      <c r="P15" s="11"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="3">
         <v>3</v>
@@ -2728,21 +2808,21 @@
       <c r="C16" s="3">
         <v>9</v>
       </c>
-      <c r="D16" s="14"/>
+      <c r="D16" s="11"/>
       <c r="E16" s="4"/>
       <c r="F16" s="3">
         <v>10</v>
       </c>
-      <c r="G16" s="14"/>
+      <c r="G16" s="11"/>
       <c r="H16" s="4"/>
       <c r="I16" s="3"/>
-      <c r="J16" s="14"/>
+      <c r="J16" s="11"/>
       <c r="K16" s="4"/>
       <c r="L16" s="3"/>
-      <c r="M16" s="14"/>
+      <c r="M16" s="11"/>
       <c r="N16" s="4"/>
       <c r="O16" s="3"/>
-      <c r="P16" s="14"/>
+      <c r="P16" s="11"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="3">
         <v>3</v>
@@ -2760,25 +2840,31 @@
       <c r="C17" s="3">
         <v>10</v>
       </c>
-      <c r="D17" s="14"/>
+      <c r="D17" s="11"/>
       <c r="E17" s="4"/>
       <c r="F17" s="3">
         <v>11</v>
       </c>
-      <c r="G17" s="14"/>
+      <c r="G17" s="11"/>
       <c r="H17" s="4"/>
       <c r="I17" s="3"/>
-      <c r="J17" s="14"/>
+      <c r="J17" s="11"/>
       <c r="K17" s="4"/>
       <c r="L17" s="3"/>
-      <c r="M17" s="14"/>
+      <c r="M17" s="11"/>
       <c r="N17" s="4"/>
       <c r="O17" s="3"/>
-      <c r="P17" s="14"/>
+      <c r="P17" s="11"/>
       <c r="Q17" s="4"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="14"/>
+      <c r="R17" s="3">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="T17" s="11">
+        <v>850</v>
+      </c>
       <c r="U17" s="2"/>
     </row>
     <row r="18" spans="2:23" ht="22" x14ac:dyDescent="0.3">
@@ -2786,25 +2872,25 @@
       <c r="C18" s="3">
         <v>11</v>
       </c>
-      <c r="D18" s="14"/>
+      <c r="D18" s="11"/>
       <c r="E18" s="4"/>
       <c r="F18" s="3">
         <v>12</v>
       </c>
-      <c r="G18" s="14"/>
+      <c r="G18" s="11"/>
       <c r="H18" s="4"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="14"/>
+      <c r="J18" s="11"/>
       <c r="K18" s="4"/>
       <c r="L18" s="3"/>
-      <c r="M18" s="14"/>
+      <c r="M18" s="11"/>
       <c r="N18" s="4"/>
       <c r="O18" s="3"/>
-      <c r="P18" s="14"/>
+      <c r="P18" s="11"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
-      <c r="T18" s="14"/>
+      <c r="T18" s="11"/>
       <c r="U18" s="2"/>
     </row>
     <row r="19" spans="2:23" ht="22" x14ac:dyDescent="0.3">
@@ -2828,7 +2914,7 @@
       <c r="Q19" s="4"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-      <c r="T19" s="14"/>
+      <c r="T19" s="11"/>
       <c r="U19" s="2"/>
     </row>
     <row r="20" spans="2:23" ht="22" x14ac:dyDescent="0.3">
@@ -2850,7 +2936,7 @@
       <c r="Q20" s="4"/>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
-      <c r="T20" s="14"/>
+      <c r="T20" s="11"/>
       <c r="U20" s="2"/>
     </row>
     <row r="21" spans="2:23" ht="22" x14ac:dyDescent="0.3">
@@ -2910,7 +2996,7 @@
       </c>
       <c r="M23" s="6">
         <f>O2-R2</f>
-        <v>33892</v>
+        <v>33829</v>
       </c>
       <c r="N23" s="4"/>
       <c r="O23" s="3"/>
@@ -2935,7 +3021,7 @@
       </c>
       <c r="M24" s="6">
         <f>C2</f>
-        <v>7650</v>
+        <v>10700</v>
       </c>
       <c r="N24" s="4"/>
       <c r="O24" s="3"/>
@@ -3024,9 +3110,9 @@
       <c r="V27">
         <v>35266</v>
       </c>
-      <c r="W27" s="15">
+      <c r="W27" s="12">
         <f>M29-V27</f>
-        <v>-6543</v>
+        <v>-3529</v>
       </c>
     </row>
     <row r="28" spans="2:23" ht="22" x14ac:dyDescent="0.3">
@@ -3044,7 +3130,7 @@
       </c>
       <c r="M28" s="6">
         <f>F2</f>
-        <v>-27</v>
+        <v>0</v>
       </c>
       <c r="N28" s="4"/>
       <c r="O28" s="3"/>
@@ -3069,7 +3155,7 @@
       </c>
       <c r="M29" s="6">
         <f>SUM(M23:M28)</f>
-        <v>28723</v>
+        <v>31737</v>
       </c>
       <c r="N29" s="4"/>
       <c r="O29" s="3"/>
@@ -3114,7 +3200,7 @@
     <row r="36" spans="26:26" x14ac:dyDescent="0.2">
       <c r="Z36">
         <f>SUM('مصاريف الشهر'!E7:E20)</f>
-        <v>1476</v>
+        <v>2007</v>
       </c>
     </row>
   </sheetData>
